--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/85.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/85.xlsx
@@ -426,13 +426,13 @@
         <v>-3.26020538576873</v>
       </c>
       <c r="E2">
-        <v>-7.630378051375689</v>
+        <v>-10.11423515666867</v>
       </c>
       <c r="F2">
-        <v>-0.5573928336106418</v>
+        <v>-1.558209762324949</v>
       </c>
       <c r="G2">
-        <v>-13.6672956890839</v>
+        <v>-18.544438102721</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.987512514535878</v>
       </c>
       <c r="E3">
-        <v>-9.346256544171977</v>
+        <v>-10.27995659495198</v>
       </c>
       <c r="F3">
-        <v>-1.245102623047389</v>
+        <v>-1.463210103469693</v>
       </c>
       <c r="G3">
-        <v>-13.94112102477823</v>
+        <v>-17.50712400805691</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.695283626588889</v>
       </c>
       <c r="E4">
-        <v>-9.459759656468217</v>
+        <v>-9.594805475906341</v>
       </c>
       <c r="F4">
-        <v>-0.9056227507669009</v>
+        <v>-1.243918886028788</v>
       </c>
       <c r="G4">
-        <v>-13.73886403056009</v>
+        <v>-17.26993264046509</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.403180617690415</v>
       </c>
       <c r="E5">
-        <v>-9.145781033522503</v>
+        <v>-11.74244766482048</v>
       </c>
       <c r="F5">
-        <v>-1.108154438914366</v>
+        <v>-1.126615434853156</v>
       </c>
       <c r="G5">
-        <v>-13.57356734751835</v>
+        <v>-17.38000163242642</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.099425360053798</v>
       </c>
       <c r="E6">
-        <v>-11.28015371225382</v>
+        <v>-12.39704360814935</v>
       </c>
       <c r="F6">
-        <v>-0.6492869430728022</v>
+        <v>-1.164779977834935</v>
       </c>
       <c r="G6">
-        <v>-12.82362965834876</v>
+        <v>-17.00810106542233</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.777299142285036</v>
       </c>
       <c r="E7">
-        <v>-11.02753878663244</v>
+        <v>-12.30784093531469</v>
       </c>
       <c r="F7">
-        <v>-0.4961566017260912</v>
+        <v>-0.8097077459315517</v>
       </c>
       <c r="G7">
-        <v>-13.08403968296165</v>
+        <v>-17.25718698537127</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.427125577890672</v>
       </c>
       <c r="E8">
-        <v>-14.12824329752294</v>
+        <v>-12.73444218975578</v>
       </c>
       <c r="F8">
-        <v>-0.6527611159601434</v>
+        <v>-0.7724047050486844</v>
       </c>
       <c r="G8">
-        <v>-12.66007956343847</v>
+        <v>-15.95011248434122</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.036043728785982</v>
       </c>
       <c r="E9">
-        <v>-12.25077165850022</v>
+        <v>-14.05339412302688</v>
       </c>
       <c r="F9">
-        <v>-0.2949005993789374</v>
+        <v>-0.5952417686119541</v>
       </c>
       <c r="G9">
-        <v>-11.87036456967868</v>
+        <v>-15.45811897151822</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.5987554911947381</v>
       </c>
       <c r="E10">
-        <v>-12.97678207055952</v>
+        <v>-15.54075046909712</v>
       </c>
       <c r="F10">
-        <v>0.7957502890667674</v>
+        <v>-0.3865553106616886</v>
       </c>
       <c r="G10">
-        <v>-11.43632175454462</v>
+        <v>-15.21579226931568</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.1067877060143828</v>
       </c>
       <c r="E11">
-        <v>-14.40305713767552</v>
+        <v>-16.44598440945675</v>
       </c>
       <c r="F11">
-        <v>-0.3477959998846998</v>
+        <v>-0.4397936552722101</v>
       </c>
       <c r="G11">
-        <v>-9.794014594292667</v>
+        <v>-14.13615408871276</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.4301508482753799</v>
       </c>
       <c r="E12">
-        <v>-15.01745414859138</v>
+        <v>-17.16355964931533</v>
       </c>
       <c r="F12">
-        <v>0.2309453711833832</v>
+        <v>-0.5422386803438277</v>
       </c>
       <c r="G12">
-        <v>-9.607360715123317</v>
+        <v>-13.85429810265617</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.005948694909929</v>
       </c>
       <c r="E13">
-        <v>-17.84109793200256</v>
+        <v>-17.49373164321655</v>
       </c>
       <c r="F13">
-        <v>-0.4133356004267938</v>
+        <v>-0.3442331916852591</v>
       </c>
       <c r="G13">
-        <v>-9.580550978917175</v>
+        <v>-12.8739139045459</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.594291209296258</v>
       </c>
       <c r="E14">
-        <v>-16.31565663808363</v>
+        <v>-19.0087899088234</v>
       </c>
       <c r="F14">
-        <v>-0.2654016077978442</v>
+        <v>-0.5921337341166504</v>
       </c>
       <c r="G14">
-        <v>-8.510756610795049</v>
+        <v>-11.54004011028807</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.179023757054089</v>
       </c>
       <c r="E15">
-        <v>-18.62719285229815</v>
+        <v>-19.09881491750038</v>
       </c>
       <c r="F15">
-        <v>0.07353237036419877</v>
+        <v>-0.7577218928340631</v>
       </c>
       <c r="G15">
-        <v>-7.864415877745428</v>
+        <v>-10.22876231046633</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.73402403787586</v>
       </c>
       <c r="E16">
-        <v>-19.36874458113497</v>
+        <v>-20.58889577019972</v>
       </c>
       <c r="F16">
-        <v>1.032113330311967</v>
+        <v>-0.373212796904797</v>
       </c>
       <c r="G16">
-        <v>-5.895994083756039</v>
+        <v>-9.676380969878579</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.247277220184106</v>
       </c>
       <c r="E17">
-        <v>-18.83772744077636</v>
+        <v>-21.45739455639124</v>
       </c>
       <c r="F17">
-        <v>0.4771742681959251</v>
+        <v>-0.4005580332386115</v>
       </c>
       <c r="G17">
-        <v>-6.482667554548062</v>
+        <v>-8.543347840898212</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.705186548432578</v>
       </c>
       <c r="E18">
-        <v>-21.0828579591182</v>
+        <v>-22.49173107078316</v>
       </c>
       <c r="F18">
-        <v>-0.3000339921740859</v>
+        <v>-0.3522004293653848</v>
       </c>
       <c r="G18">
-        <v>-3.386293140552612</v>
+        <v>-8.176895897855777</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.106985224134296</v>
       </c>
       <c r="E19">
-        <v>-20.98010751094195</v>
+        <v>-24.0787811014946</v>
       </c>
       <c r="F19">
-        <v>-0.2373365201909969</v>
+        <v>-0.3155509703633262</v>
       </c>
       <c r="G19">
-        <v>-4.663049064646062</v>
+        <v>-7.261718962025449</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.452967348223292</v>
       </c>
       <c r="E20">
-        <v>-21.29290662187141</v>
+        <v>-25.03957670295778</v>
       </c>
       <c r="F20">
-        <v>0.6828810885983206</v>
+        <v>-0.4433978818417907</v>
       </c>
       <c r="G20">
-        <v>-5.014027124496967</v>
+        <v>-6.70448424724282</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.747456668721094</v>
       </c>
       <c r="E21">
-        <v>-24.70378541413407</v>
+        <v>-25.16933133116807</v>
       </c>
       <c r="F21">
-        <v>0.3178667911265382</v>
+        <v>-0.1346968287797214</v>
       </c>
       <c r="G21">
-        <v>-3.337955204448149</v>
+        <v>-5.798441001364501</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.994292019270176</v>
       </c>
       <c r="E22">
-        <v>-24.29778408786413</v>
+        <v>-25.81831213278578</v>
       </c>
       <c r="F22">
-        <v>0.8764896030828295</v>
+        <v>-0.2322014706610428</v>
       </c>
       <c r="G22">
-        <v>-2.907305051910239</v>
+        <v>-5.668018644570846</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.194223512716324</v>
       </c>
       <c r="E23">
-        <v>-24.70844947045185</v>
+        <v>-26.36901549482407</v>
       </c>
       <c r="F23">
-        <v>1.15851888250956</v>
+        <v>-0.2178276394876658</v>
       </c>
       <c r="G23">
-        <v>-1.454725922583674</v>
+        <v>-4.629889997594332</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.348477936385336</v>
       </c>
       <c r="E24">
-        <v>-24.68543237328965</v>
+        <v>-27.07488283195796</v>
       </c>
       <c r="F24">
-        <v>0.1875770241772179</v>
+        <v>-0.1767596687590746</v>
       </c>
       <c r="G24">
-        <v>-3.196353639315347</v>
+        <v>-4.501652834023438</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.453036439612263</v>
       </c>
       <c r="E25">
-        <v>-24.48266013677755</v>
+        <v>-26.85674786675531</v>
       </c>
       <c r="F25">
-        <v>0.9258354492675961</v>
+        <v>-0.0252231062953499</v>
       </c>
       <c r="G25">
-        <v>-2.992830433970519</v>
+        <v>-3.996296225010822</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.506788395133684</v>
       </c>
       <c r="E26">
-        <v>-24.9361368217016</v>
+        <v>-27.11001069334336</v>
       </c>
       <c r="F26">
-        <v>0.593950877703377</v>
+        <v>-0.3827837538767425</v>
       </c>
       <c r="G26">
-        <v>-2.740966681776638</v>
+        <v>-4.968237275113431</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.50439373624021</v>
       </c>
       <c r="E27">
-        <v>-25.43247049428656</v>
+        <v>-28.30603795442784</v>
       </c>
       <c r="F27">
-        <v>0.2144492627240339</v>
+        <v>-0.3384445602744962</v>
       </c>
       <c r="G27">
-        <v>-2.1214239365825</v>
+        <v>-4.575218395111828</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.44431756817166</v>
       </c>
       <c r="E28">
-        <v>-24.91715249273581</v>
+        <v>-27.51820906840413</v>
       </c>
       <c r="F28">
-        <v>1.225924794810162</v>
+        <v>-0.2559814136932082</v>
       </c>
       <c r="G28">
-        <v>-1.820966395314228</v>
+        <v>-4.786083014246866</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.32452455884222</v>
       </c>
       <c r="E29">
-        <v>-27.15566279222587</v>
+        <v>-26.83545435229292</v>
       </c>
       <c r="F29">
-        <v>0.3038557848755873</v>
+        <v>-0.3738150200066322</v>
       </c>
       <c r="G29">
-        <v>-2.210087433641299</v>
+        <v>-4.520215228066253</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.146149201528221</v>
       </c>
       <c r="E30">
-        <v>-24.15642123400094</v>
+        <v>-27.69837122246387</v>
       </c>
       <c r="F30">
-        <v>1.089731253381089</v>
+        <v>-0.6972485873274908</v>
       </c>
       <c r="G30">
-        <v>-1.473136893440204</v>
+        <v>-4.942187265583303</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.913147418846123</v>
       </c>
       <c r="E31">
-        <v>-24.46944877155327</v>
+        <v>-26.64272458076425</v>
       </c>
       <c r="F31">
-        <v>1.757963640075811</v>
+        <v>-0.5008459895933393</v>
       </c>
       <c r="G31">
-        <v>-1.783854660951552</v>
+        <v>-4.841629216167393</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.63068646280685</v>
       </c>
       <c r="E32">
-        <v>-24.23856760079472</v>
+        <v>-26.78000898110646</v>
       </c>
       <c r="F32">
-        <v>0.05613582653800635</v>
+        <v>-0.3523205426387907</v>
       </c>
       <c r="G32">
-        <v>-3.009210245535164</v>
+        <v>-5.218691225228111</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.310864865601972</v>
       </c>
       <c r="E33">
-        <v>-25.36470669831066</v>
+        <v>-25.75775831166978</v>
       </c>
       <c r="F33">
-        <v>0.802320899305773</v>
+        <v>-0.5104674769768555</v>
       </c>
       <c r="G33">
-        <v>-2.197435765352763</v>
+        <v>-5.743041001141076</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.963993607651108</v>
       </c>
       <c r="E34">
-        <v>-23.17018721317318</v>
+        <v>-26.15432354180971</v>
       </c>
       <c r="F34">
-        <v>0.6783134707392842</v>
+        <v>-0.4230018196500613</v>
       </c>
       <c r="G34">
-        <v>-1.177188108080785</v>
+        <v>-5.55450346974924</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.608887954389966</v>
       </c>
       <c r="E35">
-        <v>-22.38642224443081</v>
+        <v>-25.48561498639907</v>
       </c>
       <c r="F35">
-        <v>0.7590884045536668</v>
+        <v>-0.6256958678084751</v>
       </c>
       <c r="G35">
-        <v>-2.910863496787927</v>
+        <v>-5.304913676094219</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.259068396373697</v>
       </c>
       <c r="E36">
-        <v>-23.76797968521237</v>
+        <v>-24.36101257707332</v>
       </c>
       <c r="F36">
-        <v>0.8755386373044157</v>
+        <v>-0.2704148873195867</v>
       </c>
       <c r="G36">
-        <v>-2.397687707724926</v>
+        <v>-5.959343801259403</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.93381974671392</v>
       </c>
       <c r="E37">
-        <v>-23.21335153847212</v>
+        <v>-24.99573540421289</v>
       </c>
       <c r="F37">
-        <v>0.2623496077909153</v>
+        <v>0.05631558226441384</v>
       </c>
       <c r="G37">
-        <v>-2.484152957838007</v>
+        <v>-6.023805695958582</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.642040468809963</v>
       </c>
       <c r="E38">
-        <v>-21.80143412290606</v>
+        <v>-22.67153189545764</v>
       </c>
       <c r="F38">
-        <v>1.074472725821523</v>
+        <v>-0.3958545631255159</v>
       </c>
       <c r="G38">
-        <v>-3.074544128927774</v>
+        <v>-6.151434556039746</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.394201442285404</v>
       </c>
       <c r="E39">
-        <v>-21.84763029247213</v>
+        <v>-23.16285264197353</v>
       </c>
       <c r="F39">
-        <v>1.265870327707959</v>
+        <v>-0.2614875718196165</v>
       </c>
       <c r="G39">
-        <v>-2.697706643901891</v>
+        <v>-6.415566197067268</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.189538168966378</v>
       </c>
       <c r="E40">
-        <v>-19.68849201461087</v>
+        <v>-22.16655954331704</v>
       </c>
       <c r="F40">
-        <v>0.3364139372752191</v>
+        <v>-0.2400345128219149</v>
       </c>
       <c r="G40">
-        <v>-3.394143649538089</v>
+        <v>-6.876610638134919</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.0275570550826</v>
       </c>
       <c r="E41">
-        <v>-19.69951879067829</v>
+        <v>-21.59376109703066</v>
       </c>
       <c r="F41">
-        <v>0.7905282609595192</v>
+        <v>-0.3276542464856298</v>
       </c>
       <c r="G41">
-        <v>-2.851972931046184</v>
+        <v>-7.424475390580041</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.898915117562142</v>
       </c>
       <c r="E42">
-        <v>-19.08100594733952</v>
+        <v>-21.111930438392</v>
       </c>
       <c r="F42">
-        <v>1.198954808909815</v>
+        <v>0.002916534377749307</v>
       </c>
       <c r="G42">
-        <v>-4.681791600065664</v>
+        <v>-6.898313757920843</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.794684016431392</v>
       </c>
       <c r="E43">
-        <v>-18.69597418504864</v>
+        <v>-20.03692983191868</v>
       </c>
       <c r="F43">
-        <v>0.3206757849894313</v>
+        <v>-0.05379101291569645</v>
       </c>
       <c r="G43">
-        <v>-4.047085650286339</v>
+        <v>-7.417170527214107</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.701340591913897</v>
       </c>
       <c r="E44">
-        <v>-18.27217634825181</v>
+        <v>-20.10623031608477</v>
       </c>
       <c r="F44">
-        <v>1.406734204554015</v>
+        <v>0.4975777856942797</v>
       </c>
       <c r="G44">
-        <v>-5.173648048797634</v>
+        <v>-8.102429629883453</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.605149107416496</v>
       </c>
       <c r="E45">
-        <v>-16.84851365105914</v>
+        <v>-18.31887505638818</v>
       </c>
       <c r="F45">
-        <v>0.2222002965120288</v>
+        <v>0.2234378774118113</v>
       </c>
       <c r="G45">
-        <v>-4.129564293408791</v>
+        <v>-8.150466024987642</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.492055650797239</v>
       </c>
       <c r="E46">
-        <v>-17.14018952919052</v>
+        <v>-17.80896038277103</v>
       </c>
       <c r="F46">
-        <v>0.9918646149447446</v>
+        <v>-0.1010485448780055</v>
       </c>
       <c r="G46">
-        <v>-5.345944138088154</v>
+        <v>-8.265150813386066</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.346538256511584</v>
       </c>
       <c r="E47">
-        <v>-17.56284938608434</v>
+        <v>-17.04086132714592</v>
       </c>
       <c r="F47">
-        <v>1.68704544998734</v>
+        <v>0.1213034901162434</v>
       </c>
       <c r="G47">
-        <v>-4.74613078976906</v>
+        <v>-8.790580132187458</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.157646870249277</v>
       </c>
       <c r="E48">
-        <v>-14.71143723175536</v>
+        <v>-16.90917545566958</v>
       </c>
       <c r="F48">
-        <v>0.8288849851787475</v>
+        <v>-0.1451110637677167</v>
       </c>
       <c r="G48">
-        <v>-5.466354289374891</v>
+        <v>-9.21715752316323</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.9122779148213532</v>
       </c>
       <c r="E49">
-        <v>-15.86908259038144</v>
+        <v>-15.73183141572983</v>
       </c>
       <c r="F49">
-        <v>1.664238838653464</v>
+        <v>0.2067147962840949</v>
       </c>
       <c r="G49">
-        <v>-4.759753655045489</v>
+        <v>-9.133022362597718</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.6077411786343453</v>
       </c>
       <c r="E50">
-        <v>-11.80781090465063</v>
+        <v>-14.58838588662334</v>
       </c>
       <c r="F50">
-        <v>0.456061668200774</v>
+        <v>0.207123181413675</v>
       </c>
       <c r="G50">
-        <v>-6.676964388507895</v>
+        <v>-10.05806791298246</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.2379412865768355</v>
       </c>
       <c r="E51">
-        <v>-14.21022353586373</v>
+        <v>-15.24774141013047</v>
       </c>
       <c r="F51">
-        <v>1.518422981473473</v>
+        <v>0.1014740312280289</v>
       </c>
       <c r="G51">
-        <v>-6.958491420746005</v>
+        <v>-10.48242878180037</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.188921127689661</v>
       </c>
       <c r="E52">
-        <v>-11.23610475294268</v>
+        <v>-13.90021538294455</v>
       </c>
       <c r="F52">
-        <v>0.6346866731034455</v>
+        <v>0.247125871662266</v>
       </c>
       <c r="G52">
-        <v>-7.39156956575365</v>
+        <v>-10.41111237717723</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.6704091242729512</v>
       </c>
       <c r="E53">
-        <v>-13.50794042010317</v>
+        <v>-13.4726173577855</v>
       </c>
       <c r="F53">
-        <v>0.4134512773681703</v>
+        <v>0.1863270177663934</v>
       </c>
       <c r="G53">
-        <v>-7.17844926329189</v>
+        <v>-10.78926828822162</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.188815607092852</v>
       </c>
       <c r="E54">
-        <v>-10.76352744913574</v>
+        <v>-11.64438619222995</v>
       </c>
       <c r="F54">
-        <v>0.05039938227361977</v>
+        <v>0.3588063649076953</v>
       </c>
       <c r="G54">
-        <v>-7.659413685589735</v>
+        <v>-11.18791593356167</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.734431881447075</v>
       </c>
       <c r="E55">
-        <v>-9.873701922791227</v>
+        <v>-11.10755040280526</v>
       </c>
       <c r="F55">
-        <v>0.287962727885476</v>
+        <v>0.06024452885589189</v>
       </c>
       <c r="G55">
-        <v>-6.724085717632899</v>
+        <v>-11.69416541722444</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.285149553164994</v>
       </c>
       <c r="E56">
-        <v>-8.234761669787389</v>
+        <v>-11.13293898363394</v>
       </c>
       <c r="F56">
-        <v>1.160753817762314</v>
+        <v>0.01609503138888664</v>
       </c>
       <c r="G56">
-        <v>-7.949369506740254</v>
+        <v>-12.20736731373336</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.826244623197543</v>
       </c>
       <c r="E57">
-        <v>-10.81024277011741</v>
+        <v>-11.389615749931</v>
       </c>
       <c r="F57">
-        <v>0.6318611118924964</v>
+        <v>-0.1563942561612488</v>
       </c>
       <c r="G57">
-        <v>-7.293275031898235</v>
+        <v>-12.18846552289369</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.336550421376098</v>
       </c>
       <c r="E58">
-        <v>-9.554166303092893</v>
+        <v>-9.905050361871034</v>
       </c>
       <c r="F58">
-        <v>0.6722705305358618</v>
+        <v>-0.1885672177185788</v>
       </c>
       <c r="G58">
-        <v>-9.221527909608755</v>
+        <v>-12.69907495002363</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.802071225329752</v>
       </c>
       <c r="E59">
-        <v>-8.473006484224852</v>
+        <v>-10.3922178970621</v>
       </c>
       <c r="F59">
-        <v>1.019445935988357</v>
+        <v>-0.1175579072157996</v>
       </c>
       <c r="G59">
-        <v>-9.893152398651011</v>
+        <v>-13.20205578145833</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.207954912250615</v>
       </c>
       <c r="E60">
-        <v>-7.118262175756382</v>
+        <v>-9.571381364034309</v>
       </c>
       <c r="F60">
-        <v>0.2613853881340567</v>
+        <v>-0.120803450699968</v>
       </c>
       <c r="G60">
-        <v>-9.708451356435816</v>
+        <v>-12.68731615638526</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.544780900614199</v>
       </c>
       <c r="E61">
-        <v>-7.648232706861127</v>
+        <v>-8.588507291168334</v>
       </c>
       <c r="F61">
-        <v>-0.2773367253373794</v>
+        <v>-0.105776866013185</v>
       </c>
       <c r="G61">
-        <v>-10.11122658897441</v>
+        <v>-13.0926029252205</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.805920509170036</v>
       </c>
       <c r="E62">
-        <v>-6.811040827636164</v>
+        <v>-8.224104529527878</v>
       </c>
       <c r="F62">
-        <v>0.6327971670576598</v>
+        <v>0.03084576973053744</v>
       </c>
       <c r="G62">
-        <v>-8.394938759244081</v>
+        <v>-13.0413683679922</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.987524382068973</v>
       </c>
       <c r="E63">
-        <v>-6.063205290064888</v>
+        <v>-8.521179582381539</v>
       </c>
       <c r="F63">
-        <v>0.7617077022813189</v>
+        <v>-0.4098307779455492</v>
       </c>
       <c r="G63">
-        <v>-9.241075859734714</v>
+        <v>-13.60370056158898</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.090219328967154</v>
       </c>
       <c r="E64">
-        <v>-6.010488578718839</v>
+        <v>-7.360747418956495</v>
       </c>
       <c r="F64">
-        <v>-0.2296285615079475</v>
+        <v>-0.4333514419806383</v>
       </c>
       <c r="G64">
-        <v>-8.467196337292323</v>
+        <v>-13.48895833680955</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.114298006755685</v>
       </c>
       <c r="E65">
-        <v>-4.53771000439874</v>
+        <v>-7.922029010239124</v>
       </c>
       <c r="F65">
-        <v>0.1737076687521458</v>
+        <v>-0.3517423421916366</v>
       </c>
       <c r="G65">
-        <v>-9.325201882694158</v>
+        <v>-13.71316647154976</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.064016300484409</v>
       </c>
       <c r="E66">
-        <v>-8.009541326064586</v>
+        <v>-7.472165619167671</v>
       </c>
       <c r="F66">
-        <v>-0.1094067719722525</v>
+        <v>-0.3543425874690243</v>
       </c>
       <c r="G66">
-        <v>-10.07406786120909</v>
+        <v>-13.72238239995639</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.942679742567681</v>
       </c>
       <c r="E67">
-        <v>-6.483842533043522</v>
+        <v>-8.430892921391091</v>
       </c>
       <c r="F67">
-        <v>-0.6697136548584353</v>
+        <v>-0.5245058193520987</v>
       </c>
       <c r="G67">
-        <v>-9.548746888308234</v>
+        <v>-13.73049920489017</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.756647601311182</v>
       </c>
       <c r="E68">
-        <v>-7.0542155039162</v>
+        <v>-7.999199829865763</v>
       </c>
       <c r="F68">
-        <v>-0.3476087888516671</v>
+        <v>-0.3491478954860686</v>
       </c>
       <c r="G68">
-        <v>-9.333002787532404</v>
+        <v>-14.1884342491498</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.512932391187793</v>
       </c>
       <c r="E69">
-        <v>-6.776747761727055</v>
+        <v>-8.477886507531526</v>
       </c>
       <c r="F69">
-        <v>0.187043555569815</v>
+        <v>-0.952916730894933</v>
       </c>
       <c r="G69">
-        <v>-9.522767368882064</v>
+        <v>-13.50369468465409</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.219399569547162</v>
       </c>
       <c r="E70">
-        <v>-6.446654678841007</v>
+        <v>-7.259674868155468</v>
       </c>
       <c r="F70">
-        <v>0.1483960743922041</v>
+        <v>-0.4949662377682684</v>
       </c>
       <c r="G70">
-        <v>-9.407978150699996</v>
+        <v>-13.44298312456004</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.887242792956308</v>
       </c>
       <c r="E71">
-        <v>-4.996349130999556</v>
+        <v>-7.912767348984756</v>
       </c>
       <c r="F71">
-        <v>-0.3057323315379437</v>
+        <v>-1.034713041716967</v>
       </c>
       <c r="G71">
-        <v>-10.17600568914141</v>
+        <v>-12.8576946537736</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.524010116514602</v>
       </c>
       <c r="E72">
-        <v>-7.885102808350074</v>
+        <v>-8.146327341047813</v>
       </c>
       <c r="F72">
-        <v>-0.2490960238411387</v>
+        <v>-0.7689694654292748</v>
       </c>
       <c r="G72">
-        <v>-9.153473630352204</v>
+        <v>-13.17246429689036</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.143015635715408</v>
       </c>
       <c r="E73">
-        <v>-7.338922293444521</v>
+        <v>-8.382478936977565</v>
       </c>
       <c r="F73">
-        <v>0.5649828696274782</v>
+        <v>-0.835504763589534</v>
       </c>
       <c r="G73">
-        <v>-9.490713952164672</v>
+        <v>-13.10888874997987</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.748664766454186</v>
       </c>
       <c r="E74">
-        <v>-8.051924847634462</v>
+        <v>-8.184894061410173</v>
       </c>
       <c r="F74">
-        <v>-0.6541709972797082</v>
+        <v>-0.5877334464729794</v>
       </c>
       <c r="G74">
-        <v>-8.716589019730716</v>
+        <v>-13.39005288871981</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.353494751016323</v>
       </c>
       <c r="E75">
-        <v>-8.135960925581042</v>
+        <v>-9.30415544097219</v>
       </c>
       <c r="F75">
-        <v>0.450050205958658</v>
+        <v>-1.026782252202565</v>
       </c>
       <c r="G75">
-        <v>-8.212787109122107</v>
+        <v>-12.26099200763482</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.958742101396593</v>
       </c>
       <c r="E76">
-        <v>-9.214068134125334</v>
+        <v>-9.060154275638514</v>
       </c>
       <c r="F76">
-        <v>0.3822698715919913</v>
+        <v>-1.139754998596362</v>
       </c>
       <c r="G76">
-        <v>-8.483401228969363</v>
+        <v>-11.91121750104042</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.573266807903293</v>
       </c>
       <c r="E77">
-        <v>-9.736940827075948</v>
+        <v>-10.10819223419105</v>
       </c>
       <c r="F77">
-        <v>-0.07665146813075441</v>
+        <v>-1.226642455476002</v>
       </c>
       <c r="G77">
-        <v>-8.273864173458907</v>
+        <v>-11.8161850925516</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.194817654085259</v>
       </c>
       <c r="E78">
-        <v>-7.506508523612678</v>
+        <v>-10.06670165305601</v>
       </c>
       <c r="F78">
-        <v>-0.5144105058141811</v>
+        <v>-0.9788769369312668</v>
       </c>
       <c r="G78">
-        <v>-7.525289292965882</v>
+        <v>-11.83531793428757</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.827702571053845</v>
       </c>
       <c r="E79">
-        <v>-8.070369259128025</v>
+        <v>-10.25914900621459</v>
       </c>
       <c r="F79">
-        <v>-0.2636578944149512</v>
+        <v>-0.9764249694189802</v>
       </c>
       <c r="G79">
-        <v>-6.983369205954723</v>
+        <v>-11.76582644013362</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.4680023715978257</v>
       </c>
       <c r="E80">
-        <v>-10.07622911983517</v>
+        <v>-10.96291481841811</v>
       </c>
       <c r="F80">
-        <v>-0.3663133248068799</v>
+        <v>-0.7017971527362629</v>
       </c>
       <c r="G80">
-        <v>-8.842868124858274</v>
+        <v>-11.6434412605637</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.1167850619039757</v>
       </c>
       <c r="E81">
-        <v>-12.23018003675172</v>
+        <v>-12.23254321399555</v>
       </c>
       <c r="F81">
-        <v>-0.1749571412905829</v>
+        <v>-1.011727503024087</v>
       </c>
       <c r="G81">
-        <v>-7.577647775740658</v>
+        <v>-11.70799975281275</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.2294936636263219</v>
       </c>
       <c r="E82">
-        <v>-12.57100501770112</v>
+        <v>-13.00651075722264</v>
       </c>
       <c r="F82">
-        <v>0.1715555702396727</v>
+        <v>-0.753425151115742</v>
       </c>
       <c r="G82">
-        <v>-6.687611004950455</v>
+        <v>-10.53640853696623</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.5716028251887059</v>
       </c>
       <c r="E83">
-        <v>-12.94061590634291</v>
+        <v>-14.00905443892301</v>
       </c>
       <c r="F83">
-        <v>0.08916780509203943</v>
+        <v>-0.6557680896323056</v>
       </c>
       <c r="G83">
-        <v>-7.610276861640392</v>
+        <v>-10.82504984821512</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.9109937197007304</v>
       </c>
       <c r="E84">
-        <v>-13.81368322499175</v>
+        <v>-14.68751888773567</v>
       </c>
       <c r="F84">
-        <v>0.06219119225247073</v>
+        <v>-0.7560485906804081</v>
       </c>
       <c r="G84">
-        <v>-6.160859344013665</v>
+        <v>-10.9444509467174</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.248690192801827</v>
       </c>
       <c r="E85">
-        <v>-16.57001175925011</v>
+        <v>-16.0372045848105</v>
       </c>
       <c r="F85">
-        <v>0.04794907149613883</v>
+        <v>-0.6221562538963128</v>
       </c>
       <c r="G85">
-        <v>-7.362271789952176</v>
+        <v>-10.82115461728518</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.582662543975729</v>
       </c>
       <c r="E86">
-        <v>-15.9004061101933</v>
+        <v>-17.37943111434594</v>
       </c>
       <c r="F86">
-        <v>-0.08862634730562406</v>
+        <v>-0.1400298581189446</v>
       </c>
       <c r="G86">
-        <v>-6.230339089816963</v>
+        <v>-9.884381602197166</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.912469897952276</v>
       </c>
       <c r="E87">
-        <v>-17.4572249156713</v>
+        <v>-17.53209900943531</v>
       </c>
       <c r="F87">
-        <v>0.7436675169831513</v>
+        <v>-0.436232503807575</v>
       </c>
       <c r="G87">
-        <v>-6.279269664943608</v>
+        <v>-10.11752892641736</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.231959144686709</v>
       </c>
       <c r="E88">
-        <v>-20.09411955186157</v>
+        <v>-19.83781242137243</v>
       </c>
       <c r="F88">
-        <v>0.5816106885038728</v>
+        <v>-0.3811825196871311</v>
       </c>
       <c r="G88">
-        <v>-5.93897999344872</v>
+        <v>-10.5073626980178</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.538109580564258</v>
       </c>
       <c r="E89">
-        <v>-20.52063774207616</v>
+        <v>-20.82092322728392</v>
       </c>
       <c r="F89">
-        <v>0.1842859204858955</v>
+        <v>0.05942113165750918</v>
       </c>
       <c r="G89">
-        <v>-5.3766308300121</v>
+        <v>-9.557858386931219</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.820882819679822</v>
       </c>
       <c r="E90">
-        <v>-23.47890787058166</v>
+        <v>-22.59306527389765</v>
       </c>
       <c r="F90">
-        <v>1.326904437946227</v>
+        <v>-0.1950583046869157</v>
       </c>
       <c r="G90">
-        <v>-5.035017511009518</v>
+        <v>-9.633188811363201</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.074630192846886</v>
       </c>
       <c r="E91">
-        <v>-25.3038247735</v>
+        <v>-23.56964723160651</v>
       </c>
       <c r="F91">
-        <v>0.3558722875669795</v>
+        <v>0.4648655569577272</v>
       </c>
       <c r="G91">
-        <v>-5.588020208809952</v>
+        <v>-9.415628937724254</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.288255511756155</v>
       </c>
       <c r="E92">
-        <v>-25.74265308208138</v>
+        <v>-25.3146314293672</v>
       </c>
       <c r="F92">
-        <v>1.019271978833769</v>
+        <v>0.4972157891392563</v>
       </c>
       <c r="G92">
-        <v>-5.438928417445245</v>
+        <v>-9.49554121891364</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.456921470836406</v>
       </c>
       <c r="E93">
-        <v>-27.56534801694093</v>
+        <v>-27.35455177614926</v>
       </c>
       <c r="F93">
-        <v>0.886837568678601</v>
+        <v>0.6135044902464593</v>
       </c>
       <c r="G93">
-        <v>-5.332464863764237</v>
+        <v>-9.540778895816155</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.572681628196063</v>
       </c>
       <c r="E94">
-        <v>-28.91259577896809</v>
+        <v>-28.81489978897415</v>
       </c>
       <c r="F94">
-        <v>0.9734831422766237</v>
+        <v>0.8718358350139019</v>
       </c>
       <c r="G94">
-        <v>-5.883243207173042</v>
+        <v>-9.589644202328023</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.635022845063343</v>
       </c>
       <c r="E95">
-        <v>-30.67984118942985</v>
+        <v>-31.02400535228442</v>
       </c>
       <c r="F95">
-        <v>2.030418649060985</v>
+        <v>0.8588983929169792</v>
       </c>
       <c r="G95">
-        <v>-4.796126548688879</v>
+        <v>-9.36619840500841</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.64089044809671</v>
       </c>
       <c r="E96">
-        <v>-35.48469967754664</v>
+        <v>-32.90563850905462</v>
       </c>
       <c r="F96">
-        <v>1.344469140355188</v>
+        <v>1.291622613526191</v>
       </c>
       <c r="G96">
-        <v>-4.455064096795022</v>
+        <v>-9.768634240750158</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.597213220392001</v>
       </c>
       <c r="E97">
-        <v>-38.21663224848296</v>
+        <v>-35.24462745012626</v>
       </c>
       <c r="F97">
-        <v>1.124232755707689</v>
+        <v>0.9918198831049935</v>
       </c>
       <c r="G97">
-        <v>-5.754055732570984</v>
+        <v>-9.302228635664656</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.505648312264207</v>
       </c>
       <c r="E98">
-        <v>-39.15760457229274</v>
+        <v>-37.71220604363157</v>
       </c>
       <c r="F98">
-        <v>1.466509196340028</v>
+        <v>1.48331677094283</v>
       </c>
       <c r="G98">
-        <v>-5.088965937240283</v>
+        <v>-9.850830923456769</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.383254058718912</v>
       </c>
       <c r="E99">
-        <v>-42.60436711040192</v>
+        <v>-39.3860706506659</v>
       </c>
       <c r="F99">
-        <v>1.08883495985126</v>
+        <v>1.164141840439763</v>
       </c>
       <c r="G99">
-        <v>-5.986210973846551</v>
+        <v>-9.676270013233458</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.229037131118718</v>
       </c>
       <c r="E100">
-        <v>-42.89615304863342</v>
+        <v>-41.57406336420641</v>
       </c>
       <c r="F100">
-        <v>1.62896364117265</v>
+        <v>1.728558254011235</v>
       </c>
       <c r="G100">
-        <v>-5.007876210240305</v>
+        <v>-9.885198765254184</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.072885768419047</v>
       </c>
       <c r="E101">
-        <v>-44.06479195763632</v>
+        <v>-43.45049047058093</v>
       </c>
       <c r="F101">
-        <v>1.607929736080765</v>
+        <v>1.919124175025261</v>
       </c>
       <c r="G101">
-        <v>-5.924978570206579</v>
+        <v>-9.990210744942534</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.892359328123487</v>
       </c>
       <c r="E102">
-        <v>-47.87561461745166</v>
+        <v>-46.12598297621849</v>
       </c>
       <c r="F102">
-        <v>1.849317653991347</v>
+        <v>2.088321530516671</v>
       </c>
       <c r="G102">
-        <v>-6.503154067354528</v>
+        <v>-10.26438853115666</v>
       </c>
     </row>
   </sheetData>
